--- a/UDS - Self-diagoostic program functions.xlsx
+++ b/UDS - Self-diagoostic program functions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/menghui_liu1_molex_com/Documents/Desktop/Documents/团队项目/自动诊断项目/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/menghui_liu1_molex_com/Documents/Desktop/自动诊断项目/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="126" documentId="11_F25DC773A252ABDACC10481D71DC77A65ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2C8456-5F42-496C-8384-60DF3D840F79}"/>

--- a/UDS - Self-diagoostic program functions.xlsx
+++ b/UDS - Self-diagoostic program functions.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/menghui_liu1_molex_com/Documents/Desktop/自动诊断项目/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\menghl2\WorkSpace\Projects\自动诊断项目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="11_F25DC773A252ABDACC10481D71DC77A65ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2C8456-5F42-496C-8384-60DF3D840F79}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DB020A-1C26-48A2-BDF2-5031B4813F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>System Check</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,12 +112,54 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>调光纤的数据统计分析---可以直接分析WS07的过程数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VOA事后分析 可以直接集成到MIMS软件，这样方便操作和效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PD曲线的事后分析 为什么失败 可以直接集成到MIMS里面   本身PE做了一个小工具 
+这样方便操作和效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求明细</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和盘盒技术员讨论需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE工程师 Li, Ying Zhe需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求提出时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题比较多的问题--一般是工位问题，突然就爆出测不下去操作员只能求助技术员 
+针对操作员无法解决需要找技术员的点 能否在软件层面解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,8 +182,23 @@
       <charset val="134"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,8 +211,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -177,11 +241,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -192,6 +267,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -207,6 +293,194 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1097280</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>327660</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2689860</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1318259</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A5F494-CC04-135D-7D1E-B66FFAF05313}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8176260" y="3002280"/>
+          <a:ext cx="1592580" cy="990599"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1127760</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2769900</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1079203</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{731FC42D-16D9-2A2D-D0FD-139BF99A4A69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8206740" y="1706880"/>
+          <a:ext cx="1642140" cy="942043"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1226820</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>466724</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2711400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10439</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D92691BD-FE01-E17F-8F3E-6296A52CEAD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8305800" y="466724"/>
+          <a:ext cx="1484580" cy="1113435"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -470,6 +744,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{7709326D-55E3-446E-A250-5CD324DF4918}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="zh-CN" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C9"/>
@@ -556,4 +850,80 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D934D729-FD9E-45ED-9380-968217D54BD9}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="85.5546875" customWidth="1"/>
+    <col min="3" max="3" width="82.21875" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="85.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46107</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/UDS - Self-diagoostic program functions.xlsx
+++ b/UDS - Self-diagoostic program functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\menghl2\WorkSpace\Projects\自动诊断项目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DB020A-1C26-48A2-BDF2-5031B4813F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0634F5E-C8B6-418C-A1F3-CDBAD9BE5B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>System Check</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +152,14 @@
   <si>
     <t>问题比较多的问题--一般是工位问题，突然就爆出测不下去操作员只能求助技术员 
 针对操作员无法解决需要找技术员的点 能否在软件层面解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDFA产品找hanfei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求沟通找下pengjuan</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -766,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C9"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="2" customWidth="1"/>
@@ -775,7 +783,7 @@
     <col min="4" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,8 +793,11 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -796,8 +807,11 @@
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -808,7 +822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,7 +833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -830,17 +844,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
